--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_33_R4.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_33_R4.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>M. BIRSEN</t>
+          <t>W. BALDWIN IV</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,58 +565,58 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7953</v>
+        <v>0.9039</v>
       </c>
       <c r="E2" t="n">
-        <v>1.214</v>
+        <v>2.023</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.4187</v>
+        <v>-1.1191</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.9243</v>
+        <v>3.2244</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.2451</v>
+        <v>3.9504</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.6792</v>
+        <v>-0.7261</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.921</v>
+        <v>3.7251</v>
       </c>
       <c r="K2" t="n">
-        <v>-1.0314</v>
+        <v>4.7089</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1104</v>
+        <v>-0.9838</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.0033</v>
+        <v>-0.5007</v>
       </c>
       <c r="N2" t="n">
-        <v>0.7863</v>
+        <v>-0.7584</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.7896</v>
+        <v>0.2578</v>
       </c>
       <c r="P2" t="n">
-        <v>0.6959</v>
+        <v>-0.232</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R2" t="n">
-        <v>0.6959</v>
+        <v>0.9278</v>
       </c>
       <c r="S2" t="n">
-        <v>2.0959</v>
+        <v>-1.0163</v>
       </c>
       <c r="T2" t="n">
-        <v>2.135</v>
+        <v>-0.5423</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0391</v>
+        <v>-0.474</v>
       </c>
       <c r="V2" t="n">
         <v>-1.0722</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1353</v>
+        <v>0.4384</v>
       </c>
       <c r="E3" t="n">
-        <v>0.144</v>
+        <v>0.3799</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.008699999999999999</v>
+        <v>0.0585</v>
       </c>
       <c r="G3" t="n">
         <v>0.5623</v>
@@ -688,13 +688,13 @@
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.427</v>
+        <v>-0.1239</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>0.2359</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.427</v>
+        <v>-0.3598</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>W. BALDWIN IV</t>
+          <t>A. ZAGARS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1244</v>
+        <v>0.1944</v>
       </c>
       <c r="E4" t="n">
-        <v>1.4451</v>
+        <v>-0.4899</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.3207</v>
+        <v>0.6843</v>
       </c>
       <c r="G4" t="n">
-        <v>3.2244</v>
+        <v>1.9352</v>
       </c>
       <c r="H4" t="n">
-        <v>3.9504</v>
+        <v>-0.6278</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.7261</v>
+        <v>2.563</v>
       </c>
       <c r="J4" t="n">
-        <v>3.7251</v>
+        <v>0.7023</v>
       </c>
       <c r="K4" t="n">
-        <v>4.7089</v>
+        <v>-0.8669</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.9838</v>
+        <v>1.5692</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.5007</v>
+        <v>1.2329</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.7584</v>
+        <v>0.2391</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2578</v>
+        <v>0.9939</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.232</v>
+        <v>-2.0876</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.1598</v>
+        <v>-2.3195</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9278</v>
+        <v>0.232</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.7959</v>
+        <v>-0.7255</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.1202</v>
+        <v>0.0551</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.6756</v>
+        <v>-0.7806</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.0722</v>
+        <v>1.0722</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.1123</v>
+        <v>-0.4335</v>
       </c>
       <c r="E5" t="n">
-        <v>0.067</v>
+        <v>0.2163</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.1793</v>
+        <v>-0.6498</v>
       </c>
       <c r="G5" t="n">
         <v>-1.5999</v>
@@ -844,13 +844,13 @@
         <v>1.8556</v>
       </c>
       <c r="S5" t="n">
-        <v>1.0543</v>
+        <v>0.7332</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0272</v>
+        <v>0.1221</v>
       </c>
       <c r="U5" t="n">
-        <v>1.0816</v>
+        <v>0.6111</v>
       </c>
       <c r="V5" t="n">
         <v>3.2166</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. JANTUNEN</t>
+          <t>K. BIRCH</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.5103</v>
+        <v>-0.5766</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7766999999999999</v>
+        <v>-0.5193</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.287</v>
+        <v>-0.0573</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.0321</v>
+        <v>-1.0071</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.078</v>
+        <v>-0.7261</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.9541</v>
+        <v>-0.281</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.2707</v>
+        <v>0.3729</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1547</v>
+        <v>0.3361</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.4255</v>
+        <v>0.0368</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.7613</v>
+        <v>-1.38</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.2327</v>
+        <v>-1.0622</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.5286</v>
+        <v>-0.3178</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9278</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9278</v>
+        <v>1.1598</v>
       </c>
       <c r="S6" t="n">
-        <v>1.4137</v>
+        <v>0.4305</v>
       </c>
       <c r="T6" t="n">
-        <v>0.9752</v>
+        <v>0.2675</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4384</v>
+        <v>0.163</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.8197</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.8919</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. ZAGARS</t>
+          <t>M. BIRSEN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.5702</v>
+        <v>-0.7375</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.9184</v>
+        <v>-0.0835</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3482</v>
+        <v>-0.654</v>
       </c>
       <c r="G7" t="n">
-        <v>1.9352</v>
+        <v>-0.9243</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.6278</v>
+        <v>-0.2451</v>
       </c>
       <c r="I7" t="n">
-        <v>2.563</v>
+        <v>-0.6792</v>
       </c>
       <c r="J7" t="n">
-        <v>0.7023</v>
+        <v>-0.921</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.8669</v>
+        <v>-1.0314</v>
       </c>
       <c r="L7" t="n">
-        <v>1.5692</v>
+        <v>0.1104</v>
       </c>
       <c r="M7" t="n">
-        <v>1.2329</v>
+        <v>-0.0033</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2391</v>
+        <v>0.7863</v>
       </c>
       <c r="O7" t="n">
-        <v>0.9939</v>
+        <v>-0.7896</v>
       </c>
       <c r="P7" t="n">
-        <v>-2.0876</v>
+        <v>0.6959</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.3195</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.232</v>
+        <v>0.6959</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.4901</v>
+        <v>0.5632</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3734</v>
+        <v>0.8375</v>
       </c>
       <c r="U7" t="n">
-        <v>-1.1167</v>
+        <v>-0.2743</v>
       </c>
       <c r="V7" t="n">
-        <v>1.0722</v>
+        <v>-1.0722</v>
       </c>
       <c r="W7" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>K. BIRCH</t>
+          <t>M. JANTUNEN</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.4411</v>
+        <v>-1.4719</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.4511</v>
+        <v>0.2184</v>
       </c>
       <c r="F8" t="n">
-        <v>0.009900000000000001</v>
+        <v>-1.6902</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.0071</v>
+        <v>-2.0321</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.7261</v>
+        <v>-0.078</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.281</v>
+        <v>-1.9541</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3729</v>
+        <v>-1.2707</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3361</v>
+        <v>0.1547</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0368</v>
+        <v>-1.4255</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.38</v>
+        <v>-0.7613</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.0622</v>
+        <v>-0.2327</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.3178</v>
+        <v>-0.5286</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>0.9278</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.1598</v>
+        <v>0.9278</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.434</v>
+        <v>0.452</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6642</v>
+        <v>0.4169</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2302</v>
+        <v>0.0351</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-0.8197</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.8919</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.4659</v>
+        <v>-1.9029</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.9137</v>
+        <v>-0.4852</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.5521</v>
+        <v>-1.4177</v>
       </c>
       <c r="G9" t="n">
         <v>1.383</v>
@@ -1156,13 +1156,13 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.4752</v>
+        <v>-0.9122</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4402</v>
+        <v>-0.0116</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.035</v>
+        <v>-0.9006</v>
       </c>
       <c r="V9" t="n">
         <v>-1.214</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.9011</v>
+        <v>-2.8949</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.3198</v>
+        <v>-0.717</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.5813</v>
+        <v>-2.178</v>
       </c>
       <c r="G10" t="n">
         <v>-1.2812</v>
@@ -1234,13 +1234,13 @@
         <v>0.9278</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4033</v>
+        <v>-0.3971</v>
       </c>
       <c r="T10" t="n">
-        <v>0.2715</v>
+        <v>-0.1256</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.6748</v>
+        <v>-0.2715</v>
       </c>
       <c r="V10" t="n">
         <v>-2.1444</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.0146</v>
+        <v>-3.8332</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.5096</v>
+        <v>-3.0929</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.505</v>
+        <v>-0.7403</v>
       </c>
       <c r="G11" t="n">
         <v>-5.1594</v>
@@ -1312,13 +1312,13 @@
         <v>1.6237</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2324</v>
+        <v>0.4138</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3339</v>
+        <v>0.0828</v>
       </c>
       <c r="U11" t="n">
-        <v>0.5663</v>
+        <v>0.331</v>
       </c>
       <c r="V11" t="n">
         <v>1.6083</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.4404</v>
+        <v>-5.7692</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.0015</v>
+        <v>-2.4983</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.439</v>
+        <v>-3.2709</v>
       </c>
       <c r="G12" t="n">
         <v>-3.0505</v>
@@ -1390,13 +1390,13 @@
         <v>1.1598</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.7095</v>
+        <v>-0.0382</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6642</v>
+        <v>-0.161</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0452</v>
+        <v>0.1228</v>
       </c>
       <c r="V12" t="n">
         <v>-2.6805</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-7.4013</v>
+        <v>-7.2258</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.7391</v>
+        <v>-3.6644</v>
       </c>
       <c r="F13" t="n">
-        <v>-3.6622</v>
+        <v>-3.5614</v>
       </c>
       <c r="G13" t="n">
         <v>-1.144</v>
@@ -1468,13 +1468,13 @@
         <v>0.9278</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.1672</v>
+        <v>-0.9917</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.5228</v>
+        <v>-0.4481</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.6445</v>
+        <v>-0.5436</v>
       </c>
       <c r="V13" t="n">
         <v>-2.5387</v>
@@ -1501,16 +1501,16 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-24.8022</v>
+        <v>-23.3088</v>
       </c>
       <c r="E14" t="n">
-        <v>-10.2064</v>
+        <v>-8.712900000000001</v>
       </c>
       <c r="F14" t="n">
         <v>-14.5959</v>
       </c>
       <c r="G14" t="n">
-        <v>-9.093599999999999</v>
+        <v>-9.0936</v>
       </c>
       <c r="H14" t="n">
         <v>2.4667</v>
@@ -1546,10 +1546,10 @@
         <v>10.438</v>
       </c>
       <c r="S14" t="n">
-        <v>-3.1059</v>
+        <v>-1.6122</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.7644000000000003</v>
+        <v>0.7292000000000001</v>
       </c>
       <c r="U14" t="n">
         <v>-2.3414</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. KABENGELE</t>
+          <t>K. PREPELIC</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>10.0734</v>
+        <v>9.9421</v>
       </c>
       <c r="E15" t="n">
-        <v>8.1768</v>
+        <v>7.0752</v>
       </c>
       <c r="F15" t="n">
-        <v>1.8966</v>
+        <v>2.8668</v>
       </c>
       <c r="G15" t="n">
-        <v>5.3184</v>
+        <v>6.7301</v>
       </c>
       <c r="H15" t="n">
-        <v>1.5508</v>
+        <v>1.119</v>
       </c>
       <c r="I15" t="n">
-        <v>3.7675</v>
+        <v>5.6112</v>
       </c>
       <c r="J15" t="n">
-        <v>4.8402</v>
+        <v>6.7486</v>
       </c>
       <c r="K15" t="n">
-        <v>2.6454</v>
+        <v>2.2351</v>
       </c>
       <c r="L15" t="n">
-        <v>2.1949</v>
+        <v>4.5136</v>
       </c>
       <c r="M15" t="n">
-        <v>0.4781</v>
+        <v>-0.0185</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.0945</v>
+        <v>-1.1161</v>
       </c>
       <c r="O15" t="n">
-        <v>1.5727</v>
+        <v>1.0976</v>
       </c>
       <c r="P15" t="n">
+        <v>3.0154</v>
+      </c>
+      <c r="Q15" t="n">
         <v>-0.232</v>
       </c>
-      <c r="Q15" t="n">
-        <v>-2.5515</v>
-      </c>
       <c r="R15" t="n">
-        <v>2.3195</v>
+        <v>3.2473</v>
       </c>
       <c r="S15" t="n">
-        <v>2.7008</v>
+        <v>0.1966</v>
       </c>
       <c r="T15" t="n">
-        <v>1.9935</v>
+        <v>0.5586</v>
       </c>
       <c r="U15" t="n">
-        <v>0.7073</v>
+        <v>-0.362</v>
       </c>
       <c r="V15" t="n">
-        <v>2.2862</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>3.8945</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.6083</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>K. PREPELIC</t>
+          <t>M. KABENGELE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>8.241300000000001</v>
+        <v>8.675800000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>5.7778</v>
+        <v>7.1152</v>
       </c>
       <c r="F16" t="n">
-        <v>2.4636</v>
+        <v>1.5606</v>
       </c>
       <c r="G16" t="n">
-        <v>6.7301</v>
+        <v>5.3184</v>
       </c>
       <c r="H16" t="n">
-        <v>1.119</v>
+        <v>1.5508</v>
       </c>
       <c r="I16" t="n">
-        <v>5.6112</v>
+        <v>3.7675</v>
       </c>
       <c r="J16" t="n">
-        <v>6.7486</v>
+        <v>4.8402</v>
       </c>
       <c r="K16" t="n">
-        <v>2.2351</v>
+        <v>2.6454</v>
       </c>
       <c r="L16" t="n">
-        <v>4.5136</v>
+        <v>2.1949</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.0185</v>
+        <v>0.4781</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.1161</v>
+        <v>-1.0945</v>
       </c>
       <c r="O16" t="n">
-        <v>1.0976</v>
+        <v>1.5727</v>
       </c>
       <c r="P16" t="n">
-        <v>3.0154</v>
+        <v>-0.232</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.232</v>
+        <v>-2.5515</v>
       </c>
       <c r="R16" t="n">
-        <v>3.2473</v>
+        <v>2.3195</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.5042</v>
+        <v>1.3032</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.7389</v>
+        <v>0.9320000000000001</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.7653</v>
+        <v>0.3712</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>2.2862</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>3.8945</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-1.6083</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>4.428</v>
+        <v>5.461</v>
       </c>
       <c r="E17" t="n">
-        <v>0.4093</v>
+        <v>1.117</v>
       </c>
       <c r="F17" t="n">
-        <v>4.0187</v>
+        <v>4.344</v>
       </c>
       <c r="G17" t="n">
         <v>0.4144</v>
@@ -1780,13 +1780,13 @@
         <v>3.0154</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.9142</v>
+        <v>0.1188</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.8136</v>
+        <v>-0.1059</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1006</v>
+        <v>0.2247</v>
       </c>
       <c r="V17" t="n">
         <v>2.1444</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>F. PETRUSEV</t>
+          <t>D. BACON</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>3.0115</v>
+        <v>1.963</v>
       </c>
       <c r="E18" t="n">
-        <v>2.1572</v>
+        <v>-1.0902</v>
       </c>
       <c r="F18" t="n">
-        <v>0.8542999999999999</v>
+        <v>3.0532</v>
       </c>
       <c r="G18" t="n">
-        <v>2.3042</v>
+        <v>0.0497</v>
       </c>
       <c r="H18" t="n">
-        <v>0.4236</v>
+        <v>0.3275</v>
       </c>
       <c r="I18" t="n">
-        <v>1.8806</v>
+        <v>-0.2779</v>
       </c>
       <c r="J18" t="n">
-        <v>1.7252</v>
+        <v>-0.4754</v>
       </c>
       <c r="K18" t="n">
-        <v>0.3634</v>
+        <v>0.6357</v>
       </c>
       <c r="L18" t="n">
-        <v>1.3618</v>
+        <v>-1.1112</v>
       </c>
       <c r="M18" t="n">
-        <v>0.579</v>
+        <v>0.5251</v>
       </c>
       <c r="N18" t="n">
-        <v>0.0602</v>
+        <v>-0.3082</v>
       </c>
       <c r="O18" t="n">
-        <v>0.5188</v>
+        <v>0.8333</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.4639</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.3195</v>
+        <v>-3.4793</v>
       </c>
       <c r="R18" t="n">
-        <v>1.8556</v>
+        <v>2.7834</v>
       </c>
       <c r="S18" t="n">
-        <v>2.1016</v>
+        <v>0.859</v>
       </c>
       <c r="T18" t="n">
-        <v>1.5375</v>
+        <v>0.5783</v>
       </c>
       <c r="U18" t="n">
-        <v>0.5641</v>
+        <v>0.2807</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.9304</v>
+        <v>1.7501</v>
       </c>
       <c r="W18" t="n">
-        <v>1.214</v>
+        <v>2.2862</v>
       </c>
       <c r="X18" t="n">
-        <v>-2.1444</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D. BACON</t>
+          <t>F. PETRUSEV</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.4861</v>
+        <v>1.8219</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.2081</v>
+        <v>1.2136</v>
       </c>
       <c r="F19" t="n">
-        <v>2.6942</v>
+        <v>0.6083</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0497</v>
+        <v>2.3042</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3275</v>
+        <v>0.4236</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.2779</v>
+        <v>1.8806</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.4754</v>
+        <v>1.7252</v>
       </c>
       <c r="K19" t="n">
-        <v>0.6357</v>
+        <v>0.3634</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.1112</v>
+        <v>1.3618</v>
       </c>
       <c r="M19" t="n">
-        <v>0.5251</v>
+        <v>0.579</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.3082</v>
+        <v>0.0602</v>
       </c>
       <c r="O19" t="n">
-        <v>0.8333</v>
+        <v>0.5188</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.6959</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q19" t="n">
-        <v>-3.4793</v>
+        <v>-2.3195</v>
       </c>
       <c r="R19" t="n">
-        <v>2.7834</v>
+        <v>1.8556</v>
       </c>
       <c r="S19" t="n">
-        <v>0.3822</v>
+        <v>0.912</v>
       </c>
       <c r="T19" t="n">
-        <v>0.4604</v>
+        <v>0.5939</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.07820000000000001</v>
+        <v>0.3181</v>
       </c>
       <c r="V19" t="n">
-        <v>1.7501</v>
+        <v>-0.9304</v>
       </c>
       <c r="W19" t="n">
-        <v>2.2862</v>
+        <v>1.214</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.5361</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.1398</v>
+        <v>0.7752</v>
       </c>
       <c r="E20" t="n">
-        <v>2.6546</v>
+        <v>2.3007</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.5148</v>
+        <v>-1.5256</v>
       </c>
       <c r="G20" t="n">
         <v>-2.0035</v>
@@ -2014,13 +2014,13 @@
         <v>2.0876</v>
       </c>
       <c r="S20" t="n">
-        <v>0.981</v>
+        <v>0.6163</v>
       </c>
       <c r="T20" t="n">
-        <v>0.6097</v>
+        <v>0.2559</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3712</v>
+        <v>0.3605</v>
       </c>
       <c r="V20" t="n">
         <v>1.4665</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.6747</v>
+        <v>-0.4502</v>
       </c>
       <c r="E22" t="n">
         <v>-1.2752</v>
       </c>
       <c r="F22" t="n">
-        <v>0.6004</v>
+        <v>0.8249</v>
       </c>
       <c r="G22" t="n">
         <v>-1.7406</v>
@@ -2170,13 +2170,13 @@
         <v>1.8556</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1634</v>
+        <v>0.0611</v>
       </c>
       <c r="T22" t="n">
         <v>-0.1845</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0211</v>
+        <v>0.2456</v>
       </c>
       <c r="V22" t="n">
         <v>-0.3943</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.9079</v>
+        <v>-1.6048</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.981</v>
+        <v>-0.7451</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.9268</v>
+        <v>-0.8596</v>
       </c>
       <c r="G24" t="n">
         <v>-1.208</v>
@@ -2326,13 +2326,13 @@
         <v>0.232</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.2539</v>
+        <v>0.0492</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.2987</v>
+        <v>-0.06279999999999999</v>
       </c>
       <c r="U24" t="n">
-        <v>0.0448</v>
+        <v>0.112</v>
       </c>
       <c r="V24" t="n">
         <v>-0.6778999999999999</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>24.8024</v>
+        <v>25.5889</v>
       </c>
       <c r="E25" t="n">
-        <v>14.7378</v>
+        <v>14.7376</v>
       </c>
       <c r="F25" t="n">
-        <v>10.0647</v>
+        <v>10.8511</v>
       </c>
       <c r="G25" t="n">
         <v>9.0936</v>
@@ -2377,16 +2377,16 @@
         <v>11.5602</v>
       </c>
       <c r="J25" t="n">
-        <v>9.9367</v>
+        <v>9.936700000000002</v>
       </c>
       <c r="K25" t="n">
         <v>3.329299999999999</v>
       </c>
       <c r="L25" t="n">
-        <v>6.6074</v>
+        <v>6.607400000000001</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.8431000000000002</v>
+        <v>-0.8430999999999997</v>
       </c>
       <c r="N25" t="n">
         <v>-5.7961</v>
@@ -2404,13 +2404,13 @@
         <v>17.3964</v>
       </c>
       <c r="S25" t="n">
-        <v>3.1059</v>
+        <v>3.8922</v>
       </c>
       <c r="T25" t="n">
-        <v>2.3414</v>
+        <v>2.3415</v>
       </c>
       <c r="U25" t="n">
-        <v>0.7644</v>
+        <v>1.5508</v>
       </c>
       <c r="V25" t="n">
         <v>5.6446</v>
